--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -15666,7 +15666,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32298,7 +32298,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20814,7 +20814,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31902,7 +31902,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">

--- a/diseases/d210/2000-2004.xlsx
+++ b/diseases/d210/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
